--- a/docs/评价规则与执行表确认稿-20260927.xlsx
+++ b/docs/评价规则与执行表确认稿-20260927.xlsx
@@ -11,42 +11,54 @@
     <sheet sheetId="2" name="每日报告" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="事件记录" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="填写说明" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="评价维度" state="visible" r:id="rId8"/>
+    <sheet sheetId="5" name="七项观察建议" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="人工AB规则" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="01当前点名" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="02逐人每日" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="03团级日报" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="04客观事件" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="05记录汇总" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="材料与来源" state="visible" r:id="rId15"/>
+    <sheet sheetId="7" name="S04十二项原文参考" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="01节点点名" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="02餐次记录" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="03查房记录" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="04逐人每日" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="05团级日报" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="06客观事件" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="07阶段汇总" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="08学生评价" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="材料与来源" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'事件记录'!$A$2:$J$52</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'填写说明'!$A1:$C13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'填写说明'!$A1:$C11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'填写说明'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'评价维度'!$A1:$G15</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'评价维度'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'七项观察建议'!$A1:$D10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'七项观察建议'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'人工AB规则'!$A1:$E12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'人工AB规则'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'01当前点名'!$A1:$H9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'01当前点名'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'02逐人每日'!$A1:$H9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'02逐人每日'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'03团级日报'!$A1:$H8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'03团级日报'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'04客观事件'!$A1:$H9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'04客观事件'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'05记录汇总'!$A1:$H9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'05记录汇总'!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'材料与来源'!$A1:$E12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'材料与来源'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'S04十二项原文参考'!$A1:$E15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'S04十二项原文参考'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'01节点点名'!$A1:$H8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'01节点点名'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'02餐次记录'!$A1:$H8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'02餐次记录'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'03查房记录'!$A1:$H8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'03查房记录'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'04逐人每日'!$A1:$H9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'04逐人每日'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'05团级日报'!$A1:$H8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'05团级日报'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'06客观事件'!$A1:$H8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'06客观事件'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'07阶段汇总'!$A1:$H8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'07阶段汇总'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'08学生评价'!$A1:$H9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'08学生评价'!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'材料与来源'!$A1:$D16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'材料与来源'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="421">
   <si>
     <t>逐人点名与信息核对。健康信息只在家长授权后由有权限人员查看，不写入本表。</t>
   </si>
@@ -132,117 +144,271 @@
     <t>处置过程</t>
   </si>
   <si>
-    <t>评价规则与执行表｜需求方确认稿</t>
-  </si>
-  <si>
-    <t>2026-09-27 草案。所有单元格可编辑，浅黄色为重点确认栏；填写此工作簿不会自动导入或启用系统规则。</t>
-  </si>
-  <si>
-    <t>确认事项</t>
-  </si>
-  <si>
-    <t>现有依据或填写说明</t>
+    <t>评价规则与八类执行表｜可编辑确认稿</t>
+  </si>
+  <si>
+    <t>A=优秀、B=合格及逐人手评已确认。其余建议可改；黄色栏可试填和反馈，所有单元格均可编辑。</t>
+  </si>
+  <si>
+    <t>事项</t>
+  </si>
+  <si>
+    <t>说明</t>
   </si>
   <si>
     <t>需求方修改/确认</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>本稿供需求方直接修改。A=优秀、B=合格，以及由导游逐名学生手动选择，已经确认；下列观察说明、执行字段建议、填写责任与时间仍是可调整草案。填写文件不会自动导入或启用系统配置。</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>评价对象是本团有效、无名单冲突的学生；教师和陪同不计入应评人数。每人初始为未评价，导游查看实际表现后选择A或B；没有异常、缺席或没有评语均不能自动推导等级。全部应评学生完成后再确认，修改评级或观察后需重新确认。学校只输出已确认的A/B结果，不输出内部观察或私人正文。</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>七项观察建议用于辅助判断，不要求逐项打分、固定满足几项、设置权重或优秀比例。B（合格）的建议说明为“完成本次活动基本要求”；A（优秀）的建议说明为“完成基本要求，并在参与、合作、观察探究或成果表达等方面有实际观察到的突出表现”。等级名称已确认，以上表现说明仍可修改。没有相应活动或未观察到时，不据此判断表现差。</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>八类表由现有材料整理，是实施草案，不是已经取得并逐张还原的客户七八张原表。字段、必填、填写人、复核人、时间与公开范围均可在黄色栏修订；复核责任建议不新增系统审批层级。工作簿同时提供各字段试填栏，不填写真实个人证件、电话或健康正文。</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>会议确实提到小包团每天三餐、住宿安全、身体情况和三次查房。三次查房仅作为住宿小包团的可选建议，具体时点可改；各团期须按实际日期、行程显式确认应填节点。出发、抵达、返程是可修改的点名建议。一日团不自动套三餐、住宿或三次查房。S08大明山告家长书已载11:30自带午餐、无住宿，其活动时点不自动等于必填检查点。</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>新记录按实际节点和发生时间保存；更正保留前记录和原因。已有点名快照、综合用餐和住宿文字继续保留，不把旧文字猜拆为三餐或查房历史。应填、已填、未填按已确认计划节点的当前版本与当前有效确认人员核对；已填只统计明确关联该节点及版本的发生记录。个人日报三餐是当日汇总，不自动同步为节点记录；计划内餐次和查房仍须在执行节点中记录。没有计划时只展示已记录事实，不虚构完成率。</t>
+  </si>
+  <si>
     <t>适用范围</t>
   </si>
   <si>
-    <t>请填写课程、年级、团型及有效日期；不同团型可以分别确认，不默认一套规则通用。</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>如何修改</t>
-  </si>
-  <si>
-    <t>先改“评价维度”名称/观察建议及“人工AB规则”；再逐字段修改五组执行建议。可直接覆盖建议，并在末栏写同意/修改及修改理由。</t>
-  </si>
-  <si>
-    <t>评价边界</t>
-  </si>
-  <si>
-    <t>导游主评，不恢复学生自评或要求老师逐人打分。本确认稿只需填写名称和说明，O01—O12用于对应稿件条目，不是系统编码。</t>
-  </si>
-  <si>
-    <t>权重与阈值</t>
-  </si>
-  <si>
-    <t>本稿留空，不自动评分。若确定仅人工判定，请在权重/阈值栏明确“不采用”，不要把空白解释为0或等权。</t>
-  </si>
-  <si>
-    <t>原表与草案</t>
-  </si>
-  <si>
-    <t>前三张表是已有开发方03模板参考页；随后五组为确认建议，不是甲方完整7—8张官方原表。</t>
-  </si>
-  <si>
-    <t>点名与用餐口径</t>
-  </si>
-  <si>
-    <t>点名只含当前状态和最后更新时间，非历史多次点名。团级及逐人用餐均为单一文字字段，不是三餐结构化明细。</t>
-  </si>
-  <si>
-    <t>可见范围</t>
-  </si>
-  <si>
-    <t>详细学生观察、健康和私人事件正文不进入学校报告或普通管理汇总；家属只看确认范围内已批准摘要。</t>
-  </si>
-  <si>
-    <t>已提供材料</t>
-  </si>
-  <si>
-    <t>S04课程时间安排及观察表、S05车辆联系单已收到，不重复索取；其余现行执行原表和正式学校/教育部门表需逐字段确认。</t>
-  </si>
-  <si>
-    <t>确认人/职务</t>
-  </si>
-  <si>
-    <t>由需求方指定能确认该业务规则的负责人填写。</t>
-  </si>
-  <si>
-    <t>确认日期/版本</t>
-  </si>
-  <si>
-    <t>需填写版本、日期及适用范围后，再由双方核对系统配置；本文件本身不是正式生效凭证。</t>
-  </si>
-  <si>
-    <t>四类十二项观察内容｜候选维度</t>
-  </si>
-  <si>
-    <t>原文保留供核对；维度名称及观察说明是我方建议。权重、阈值留空待确认。原表自评/组评/师评列不移植为系统角色。</t>
-  </si>
-  <si>
-    <t>序号/来源</t>
-  </si>
-  <si>
-    <t>类别/维度建议</t>
-  </si>
-  <si>
-    <t>S04观察原文</t>
-  </si>
-  <si>
-    <t>导游观察说明建议</t>
-  </si>
-  <si>
-    <t>需求方改写/确认</t>
-  </si>
-  <si>
-    <t>权重确认</t>
-  </si>
-  <si>
-    <t>阈值确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">O01
-S04 T5R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参与态度
-学习投入</t>
+    <t>课程/年级/团型/日期范围：</t>
+  </si>
+  <si>
+    <t>确认人及版本</t>
+  </si>
+  <si>
+    <t>确认人/职务/确认日期/生效版本：</t>
+  </si>
+  <si>
+    <t>七项现场观察建议｜初稿</t>
+  </si>
+  <si>
+    <t>依据实际活动观察，不打分、不按项数推导A/B；不是教育局官方评分表。没有观察机会不作负面判断。</t>
+  </si>
+  <si>
+    <t>建议指标</t>
+  </si>
+  <si>
+    <t>可观察的具体表现</t>
+  </si>
+  <si>
+    <t>依据</t>
+  </si>
+  <si>
+    <t>遵守安全提示</t>
+  </si>
+  <si>
+    <t>听取乘车和活动安全说明，按要求使用器材，需要帮助时及时告知导游或老师。</t>
+  </si>
+  <si>
+    <t>S08 P10/P12；浙江课程指南</t>
+  </si>
+  <si>
+    <t>遵守集合与活动安排</t>
+  </si>
+  <si>
+    <t>按集合要求归队，随集体行动，有事先向带队人员说明。</t>
+  </si>
+  <si>
+    <t>S08 P10；浙江课程指南</t>
+  </si>
+  <si>
+    <t>参与研学活动</t>
+  </si>
+  <si>
+    <t>参与参观、体验或实践任务，愿意尝试适合自己的活动。</t>
+  </si>
+  <si>
+    <t>教育部2016意见；S04 T5R2</t>
+  </si>
+  <si>
+    <t>认真观察与学习</t>
+  </si>
+  <si>
+    <t>留意讲解和现场事物，通过观察、提问、记录等方式了解学习内容。</t>
+  </si>
+  <si>
+    <t>浙江课程指南；S04 T5R3/R11</t>
+  </si>
+  <si>
+    <t>与同伴合作</t>
+  </si>
+  <si>
+    <t>参与分工，听取同伴意见，愿意帮助他人并共同完成任务。</t>
+  </si>
+  <si>
+    <t>浙江课程指南；S04 T5R4—7</t>
+  </si>
+  <si>
+    <t>爱护环境与公共设施</t>
+  </si>
+  <si>
+    <t>保持活动场所整洁，爱护物品和设施，用餐文明。</t>
+  </si>
+  <si>
+    <t>S08 P13；浙江课程指南</t>
+  </si>
+  <si>
+    <t>表达与分享收获</t>
+  </si>
+  <si>
+    <t>用口述、记录、作品等适合自己的方式分享发现或活动感受。</t>
+  </si>
+  <si>
+    <t>教育部2017纲要；S04 T5R6/R10</t>
+  </si>
+  <si>
+    <t>人工A/B｜名称及逐人选择已确认</t>
+  </si>
+  <si>
+    <t>A=优秀、B=合格已确认；表现说明仍为可编辑建议。无分数线、权重、自动转换或优秀名额比例。</t>
+  </si>
+  <si>
+    <t>状态/事项</t>
+  </si>
+  <si>
+    <t>现有口径</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>需求方补充/修改</t>
+  </si>
+  <si>
+    <t>确认人/日期</t>
+  </si>
+  <si>
+    <t>已确认：名称</t>
+  </si>
+  <si>
+    <t>A=优秀；B=合格。</t>
+  </si>
+  <si>
+    <t>用户本轮确认</t>
+  </si>
+  <si>
+    <t>已确认：逐人选择</t>
+  </si>
+  <si>
+    <t>导游逐名有效学生人工选择A或B；不默认A、不批量填入同一等级。</t>
+  </si>
+  <si>
+    <t>用户本轮确认，优先于旧“批量后修改”口径</t>
+  </si>
+  <si>
+    <t>建议：B表现说明</t>
+  </si>
+  <si>
+    <t>完成本次活动基本要求。</t>
+  </si>
+  <si>
+    <t>本稿建议，可改</t>
+  </si>
+  <si>
+    <t>建议：A表现说明</t>
+  </si>
+  <si>
+    <t>完成基本要求，并在参与、合作、观察探究或成果表达等方面有实际观察到的突出表现。</t>
+  </si>
+  <si>
+    <t>观察建议</t>
+  </si>
+  <si>
+    <t>七项可编辑或删除；需主动加载、保存并确认标准后生效。按实际活动和年龄观察，不逐项强制评分。S04十二项仅作原文参照。</t>
+  </si>
+  <si>
+    <t>本稿及来源核对第5—6节</t>
+  </si>
+  <si>
+    <t>应评与未评</t>
+  </si>
+  <si>
+    <t>有效、无名单冲突的学生为应评对象；教师/陪同不计；未选等级保持未评价，全部应评完成才确认。</t>
+  </si>
+  <si>
+    <t>本轮实施口径</t>
+  </si>
+  <si>
+    <t>学校与家庭边界</t>
+  </si>
+  <si>
+    <t>学校仅已确认A/B，内部观察不导出；家庭服务摘要沿用单独批准范围。</t>
+  </si>
+  <si>
+    <t>S39 P93—94；S40 04表B13:F13</t>
+  </si>
+  <si>
+    <t>修改与版本</t>
+  </si>
+  <si>
+    <t>评级或观察修改后重新确认；旧已确认标准不静默改写；文件编辑不自动启用。</t>
+  </si>
+  <si>
+    <t>不采用自动评分</t>
+  </si>
+  <si>
+    <t>无权重、分数线、固定达标项数或A名额比例。</t>
+  </si>
+  <si>
+    <t>用户逐人手评要求</t>
+  </si>
+  <si>
+    <t>S04原文参考｜四类十二项</t>
+  </si>
+  <si>
+    <t>仅留作课程来源核对，不与七项建议并列强制填写；原自评/组评/师评不恢复为系统入口。疑似“猪肚”错字仅照录。</t>
+  </si>
+  <si>
+    <t>序号/定位</t>
+  </si>
+  <si>
+    <t>类别/维度</t>
+  </si>
+  <si>
+    <t>原文</t>
+  </si>
+  <si>
+    <t>导游观察参考</t>
+  </si>
+  <si>
+    <t>需求方补充</t>
+  </si>
+  <si>
+    <t>O01 / S04 T5R2</t>
+  </si>
+  <si>
+    <t>参与态度 / 学习投入</t>
   </si>
   <si>
     <t>1.我能认真参与每一项学习，对每一项学习始终保持浓厚的兴趣。</t>
@@ -251,12 +417,10 @@
     <t>记录实际参与的环节、持续投入的表现；未观察到的环节不作推断。</t>
   </si>
   <si>
-    <t xml:space="preserve">O02
-S04 T5R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参与态度
-主动学习与交流</t>
+    <t>O02 / S04 T5R3</t>
+  </si>
+  <si>
+    <t>参与态度 / 主动学习与交流</t>
   </si>
   <si>
     <t>2.我能积极学习各种知识，猪肚与他人交流。</t>
@@ -265,12 +429,10 @@
     <t>记录提问、分享或交流的具体表现。原文“猪肚”疑为“主动”，请确认后改写，不静默替换原文。</t>
   </si>
   <si>
-    <t xml:space="preserve">O03
-S04 T5R4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">参与态度
-承担小组任务</t>
+    <t>O03 / S04 T5R4</t>
+  </si>
+  <si>
+    <t>参与态度 / 承担小组任务</t>
   </si>
   <si>
     <t>3.我能发挥自身优势为小组提供必不可少的帮助，努力完成自己承担的任务。</t>
@@ -279,12 +441,10 @@
     <t>记录所承担的任务、实际完成情况和给予小组的帮助。</t>
   </si>
   <si>
-    <t xml:space="preserve">O04
-S04 T5R5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">协作精神
-配合活动安排</t>
+    <t>O04 / S04 T5R5</t>
+  </si>
+  <si>
+    <t>协作精神 / 配合活动安排</t>
   </si>
   <si>
     <t>4.积极配合小组开展活动，服从安排。</t>
@@ -293,12 +453,10 @@
     <t>记录配合任务分工、遵守已说明活动安排的事实，不用笼统负面标签代替记录。</t>
   </si>
   <si>
-    <t xml:space="preserve">O05
-S04 T5R6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">协作精神
-表达与尊重</t>
+    <t>O05 / S04 T5R6</t>
+  </si>
+  <si>
+    <t>协作精神 / 表达与尊重</t>
   </si>
   <si>
     <t>5.积极地与组内、组间成员交互讨论，能完整清晰地表达想法，尊重他人的意见和成果。</t>
@@ -307,12 +465,10 @@
     <t>记录表达想法、倾听回应和尊重他人成果的具体场景。</t>
   </si>
   <si>
-    <t xml:space="preserve">O06
-S04 T5R7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">协作精神
-互助学习</t>
+    <t>O06 / S04 T5R7</t>
+  </si>
+  <si>
+    <t>协作精神 / 互助学习</t>
   </si>
   <si>
     <t>6.和大家能互相学习和帮助，促进共同进步。</t>
@@ -321,12 +477,10 @@
     <t>记录向他人学习、提供帮助或共同完成任务的例子。</t>
   </si>
   <si>
-    <t xml:space="preserve">O07
-S04 T5R8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">创新实践
-好奇与探索</t>
+    <t>O07 / S04 T5R8</t>
+  </si>
+  <si>
+    <t>创新实践 / 好奇与探索</t>
   </si>
   <si>
     <t>7.我有浓厚的好奇心和探索欲望。</t>
@@ -335,12 +489,10 @@
     <t>记录提出的问题和实际尝试；不从安静或发言少直接推断缺少兴趣。</t>
   </si>
   <si>
-    <t xml:space="preserve">O08
-S04 T5R9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">创新实践
-提出解决办法</t>
+    <t>O08 / S04 T5R9</t>
+  </si>
+  <si>
+    <t>创新实践 / 提出解决办法</t>
   </si>
   <si>
     <t>8.小组遇到问题时，我能提出合理的解决方法。</t>
@@ -349,12 +501,10 @@
     <t>记录遇到的问题、提出的办法及尝试结果；是否采用不直接等同优劣。</t>
   </si>
   <si>
-    <t xml:space="preserve">O09
-S04 T5R10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">创新实践
-发挥个性特长</t>
+    <t>O09 / S04 T5R10</t>
+  </si>
+  <si>
+    <t>创新实践 / 发挥个性特长</t>
   </si>
   <si>
     <t>9.活动中，我能发挥个性特长，施展才华。</t>
@@ -363,12 +513,10 @@
     <t>记录在任务中使用的特长及形成的作品或贡献，不比较无观察机会的能力。</t>
   </si>
   <si>
-    <t xml:space="preserve">O10
-S04 T5R11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能力提高
-多渠道收集信息</t>
+    <t>O10 / S04 T5R11</t>
+  </si>
+  <si>
+    <t>能力提高 / 多渠道收集信息</t>
   </si>
   <si>
     <t>10在活动中，我能运用多种渠道收集信息。</t>
@@ -377,12 +525,10 @@
     <t>记录实际使用的观察、访问、阅读等渠道以及如何整理所得信息。</t>
   </si>
   <si>
-    <t xml:space="preserve">O11
-S04 T5R12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能力提高
-独立应对问题</t>
+    <t>O11 / S04 T5R12</t>
+  </si>
+  <si>
+    <t>能力提高 / 独立应对问题</t>
   </si>
   <si>
     <t>11.我遇到问题不退缩，并能自己想办法解决。</t>
@@ -391,12 +537,10 @@
     <t>记录尝试、求助与调整办法的过程；安全问题应及时求助，不以冒险独立处理作为优秀依据。</t>
   </si>
   <si>
-    <t xml:space="preserve">O12
-S04 T5R13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">能力提高
-交往能力变化</t>
+    <t>O12 / S04 T5R13</t>
+  </si>
+  <si>
+    <t>能力提高 / 交往能力变化</t>
   </si>
   <si>
     <t>12.我与他人交往的能力提高了。</t>
@@ -405,652 +549,778 @@
     <t>记录本次活动中可观察的交流合作变化；缺少前后对照时只写当次表现，不宣称能力提高。</t>
   </si>
   <si>
-    <t>人工A/B定义与生效条件｜待确认</t>
-  </si>
-  <si>
-    <t>没有正式定义前不预填A/B，不从观察项推导等级；未评价不自动A。请在确认栏写具体内容，不能只用“按原规则”而不附原规则。</t>
-  </si>
-  <si>
-    <t>待确认事项</t>
-  </si>
-  <si>
-    <t>现有原则/建议</t>
-  </si>
-  <si>
-    <t>来源</t>
-  </si>
-  <si>
-    <t>需求方正式定义/修改</t>
-  </si>
-  <si>
-    <t>确认人/日期</t>
-  </si>
-  <si>
-    <t>评价主体</t>
-  </si>
-  <si>
-    <t>按会议口径由导游主评，可批量填写后逐人调整；不要求学生自评，不增加老师逐人评价负担。</t>
-  </si>
-  <si>
-    <t>S39 P92；S40 04表B12:F12</t>
-  </si>
-  <si>
-    <t>正式A定义</t>
-  </si>
-  <si>
-    <t>请填写人工判定A所需表现、证据与例外；本稿不预填“优秀”等同义标签。</t>
-  </si>
-  <si>
-    <t>S39 P95；S40 13表B10:F10</t>
-  </si>
-  <si>
-    <t>正式B定义</t>
-  </si>
-  <si>
-    <t>请填写人工判定B所需表现、证据与例外；本稿不预设分数下限或人数比例。</t>
-  </si>
-  <si>
-    <t>人工判定方法</t>
-  </si>
-  <si>
-    <t>建议先记观察事实，再由有权限人员按确认定义选择A/B；请明确填写者和最终确认者。</t>
-  </si>
-  <si>
-    <t>我方建议，未生效</t>
-  </si>
-  <si>
-    <t>未观察/未评价</t>
-  </si>
-  <si>
-    <t>建议保持未评价，不自动转A；是否需要补评及由谁补评，请填写。</t>
-  </si>
-  <si>
-    <t>S39 P95（含数据检查建议）</t>
-  </si>
-  <si>
-    <t>权重与数值阈值</t>
-  </si>
-  <si>
-    <t>留空待确认；本稿不设加权总分、及格线、A比例或自动转换算法。</t>
+    <t>节点点名表（草案）</t>
+  </si>
+  <si>
+    <t>S39 P83；S40 04表B6:F6；会议点名讨论。出发/抵达/返程为建议，可按行程修改。</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <t>字段说明</t>
+  </si>
+  <si>
+    <t>必填建议</t>
+  </si>
+  <si>
+    <t>复核责任建议</t>
+  </si>
+  <si>
+    <t>公开范围</t>
+  </si>
+  <si>
+    <t>填写时间</t>
+  </si>
+  <si>
+    <t>试填值/需求方修改</t>
+  </si>
+  <si>
+    <t>团期、人员、当前车辆</t>
+  </si>
+  <si>
+    <t>按有效确认的人车名单带出；班级、姓名、类型沿用名单。</t>
+  </si>
+  <si>
+    <t>系统带出</t>
+  </si>
+  <si>
+    <t>系统/负责导游</t>
+  </si>
+  <si>
+    <t>运营核对</t>
+  </si>
+  <si>
+    <t>内部</t>
+  </si>
+  <si>
+    <t>每次点名</t>
+  </si>
+  <si>
+    <t>日期、节点、计划时间</t>
+  </si>
+  <si>
+    <t>选择本团已确认点名节点；计划时间可空，标签可改。额外发生记录可单列。</t>
+  </si>
+  <si>
+    <t>日期/节点必填；时间可选</t>
+  </si>
+  <si>
+    <t>管理者设计划；导游选节点</t>
+  </si>
+  <si>
+    <t>执行负责人</t>
+  </si>
+  <si>
+    <t>出发前设计划；实际点名时记录</t>
+  </si>
+  <si>
+    <t>实际发生时间、到场状态</t>
+  </si>
+  <si>
+    <t>到场/未到/撤销；逐人选择并保留历次结果，不把最新快照当全部历史。</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>负责导游</t>
+  </si>
+  <si>
+    <t>不直接公开明细</t>
+  </si>
+  <si>
+    <t>该节点点名时</t>
+  </si>
+  <si>
+    <t>地点、客观说明</t>
+  </si>
+  <si>
+    <t>按需记地点和必要服务事实；不写健康或私人正文。</t>
+  </si>
+  <si>
+    <t>按需</t>
+  </si>
+  <si>
+    <t>发现情况时</t>
+  </si>
+  <si>
+    <t>更正关联、原因、版本、记录人</t>
+  </si>
+  <si>
+    <t>更正追加并关联前记录；原记录保留，系统记录操作者及时间。</t>
+  </si>
+  <si>
+    <t>更正时原因必填；其余系统记录</t>
+  </si>
+  <si>
+    <t>运营追溯</t>
+  </si>
+  <si>
+    <t>更正时</t>
+  </si>
+  <si>
+    <t>逐人餐次记录表（草案）</t>
+  </si>
+  <si>
+    <t>会议01:35:10—01:35:43；S39 P87；S08 11:30午餐安排。适用餐次由实际团期决定。</t>
+  </si>
+  <si>
+    <t>团期、人员、日期</t>
+  </si>
+  <si>
+    <t>按有效确认名单记录每名参加人适用餐次。</t>
+  </si>
+  <si>
+    <t>必填/带出</t>
+  </si>
+  <si>
+    <t>用餐后</t>
+  </si>
+  <si>
+    <t>餐次、节点标签、计划时间</t>
+  </si>
+  <si>
+    <t>早餐/午餐/晚餐分开；本团适用的餐次才加入计划，标签可改、时间可空。</t>
+  </si>
+  <si>
+    <t>餐次/标签必填</t>
+  </si>
+  <si>
+    <t>管理者设计划；导游填报</t>
+  </si>
+  <si>
+    <t>行前设定；用餐后填报</t>
+  </si>
+  <si>
+    <t>实际发生时间、记录状态</t>
+  </si>
+  <si>
+    <t>已记录/不适用；未填保持空白，不把不适用等同已用餐。</t>
+  </si>
+  <si>
+    <t>原始明细不直接公开</t>
+  </si>
+  <si>
+    <t>各适用餐次后</t>
+  </si>
+  <si>
+    <t>地点、用餐说明</t>
+  </si>
+  <si>
+    <t>记录必要的餐饮服务事实；自带/自理等实际安排可说明。</t>
+  </si>
+  <si>
+    <t>经单独批准的摘要可公开</t>
+  </si>
+  <si>
+    <t>更正与日报口径</t>
+  </si>
+  <si>
+    <t>更正保留原因、前记录、版本和操作者；个人日报独立汇总三餐，不自动同步或推定关联计划节点，旧综合用餐文字保留。</t>
+  </si>
+  <si>
+    <t>更正原因必填；关联系统记录</t>
+  </si>
+  <si>
+    <t>发生更正或每日整理时</t>
+  </si>
+  <si>
+    <t>逐人查房记录表（草案）</t>
+  </si>
+  <si>
+    <t>会议三次查房为小包团举例；S39 P87—88。仅住宿团期按实际安排适用。</t>
+  </si>
+  <si>
+    <t>按有住宿安排的团期及有效人员记录。</t>
+  </si>
+  <si>
+    <t>实际查房时</t>
+  </si>
+  <si>
+    <t>查房节点、计划时间</t>
+  </si>
+  <si>
+    <t>每次独立节点；三次查房为可选建议，次数与时点可调整，无统一强制三次。</t>
+  </si>
+  <si>
+    <t>节点必填；时间可空</t>
+  </si>
+  <si>
+    <t>管理者设计划</t>
+  </si>
+  <si>
+    <t>住宿安排明确后</t>
+  </si>
+  <si>
+    <t>实际发生时间、状态</t>
+  </si>
+  <si>
+    <t>已记录/不适用；具体在场、安全核对情况写必要说明，不用餐次状态推断住宿。</t>
+  </si>
+  <si>
+    <t>明细默认内部</t>
+  </si>
+  <si>
+    <t>每次查房后</t>
+  </si>
+  <si>
+    <t>地点、查房说明</t>
+  </si>
+  <si>
+    <t>可填写必要住宿区域及实际核对结果；不公开房号或私人细节。</t>
+  </si>
+  <si>
+    <t>有权人员</t>
+  </si>
+  <si>
+    <t>仅另行批准的服务摘要</t>
+  </si>
+  <si>
+    <t>查房时</t>
+  </si>
+  <si>
+    <t>更正原因、前记录、记录人及时间</t>
+  </si>
+  <si>
+    <t>同一天多次和额外查房分别保留，更正不覆盖旧行。旧住宿综合文字仍是历史原文。</t>
+  </si>
+  <si>
+    <t>更正原因必填；其余系统记录</t>
+  </si>
+  <si>
+    <t>逐人每日记录表（草案）</t>
+  </si>
+  <si>
+    <t>S39 P87；S40 04表B7:F8；沿用个人日报及受限摘要机制，不替代逐次发生记录。</t>
+  </si>
+  <si>
+    <t>一人一日，名单归属和记录日期按实际行程核对。</t>
+  </si>
+  <si>
+    <t>本人家庭只见批准摘要</t>
+  </si>
+  <si>
+    <t>每日整理时</t>
+  </si>
+  <si>
+    <t>早餐/午餐/晚餐状态与各餐说明</t>
+  </si>
+  <si>
+    <t>各餐独立为空/已记录/不适用，分别填写说明；空白仍是未填。此处仅汇总当天情况，填写日报不完成计划节点；计划内餐次和查房须另在执行节点中记录。</t>
+  </si>
+  <si>
+    <t>适用餐次建议填</t>
+  </si>
+  <si>
+    <t>仅批准摘要</t>
+  </si>
+  <si>
+    <t>当餐后或当日整理</t>
+  </si>
+  <si>
+    <t>住宿核对、历史用餐文字</t>
+  </si>
+  <si>
+    <t>保留既有综合住宿、用餐文字；不能据旧文字生成逐次事实。</t>
+  </si>
+  <si>
+    <t>适用时填</t>
+  </si>
+  <si>
+    <t>每日整理</t>
+  </si>
+  <si>
+    <t>身体情况/私人备注入口</t>
+  </si>
+  <si>
+    <t>仅现有受限入口处理，需有效授权、相应权限和负责范围；本确认稿不采集正文。</t>
+  </si>
+  <si>
+    <t>按需，不强制</t>
+  </si>
+  <si>
+    <t>满足权限和授权的负责人员</t>
+  </si>
+  <si>
+    <t>普通管理及导出不含正文</t>
+  </si>
+  <si>
+    <t>确需记录时</t>
+  </si>
+  <si>
+    <t>拟公开摘要、批准状态</t>
+  </si>
+  <si>
+    <t>摘要单独拟稿和批准；事实修改后撤销旧公开状态，重新批准。</t>
+  </si>
+  <si>
+    <t>拟公开时必填</t>
+  </si>
+  <si>
+    <t>负责导游拟稿</t>
+  </si>
+  <si>
+    <t>有发布权限的人员</t>
+  </si>
+  <si>
+    <t>仅本订单相应人员</t>
+  </si>
+  <si>
+    <t>公开前</t>
+  </si>
+  <si>
+    <t>版本、更正原因、更新人/时间</t>
+  </si>
+  <si>
+    <t>版本用于防止覆盖他人修改；更正原因记录变更缘由。</t>
+  </si>
+  <si>
+    <t>修改时原因/版本必需</t>
+  </si>
+  <si>
+    <t>负责人员/系统</t>
+  </si>
+  <si>
+    <t>团级每日报告（草案）</t>
+  </si>
+  <si>
+    <t>已有03模板“每日报告”；S39 P85/P87。保持全团服务总结，不替代逐人明细。</t>
+  </si>
+  <si>
+    <t>团期、日期、填写人</t>
+  </si>
+  <si>
+    <t>记录团队当日服务情况；责任人由本团安排。</t>
+  </si>
+  <si>
+    <t>建议必填</t>
+  </si>
+  <si>
+    <t>每日；具体截止时间由本团定</t>
+  </si>
+  <si>
+    <t>住宿核对、用餐情况</t>
+  </si>
+  <si>
+    <t>团级保留概括文字，适用时填；各餐与查房次数从逐人逐次事实核对。</t>
+  </si>
+  <si>
+    <t>适用时建议填</t>
+  </si>
+  <si>
+    <t>当日整理</t>
+  </si>
+  <si>
+    <t>其他服务记录</t>
+  </si>
+  <si>
+    <t>写去标识的服务事实；个人健康和私人事件正文留受限入口。</t>
+  </si>
+  <si>
+    <t>原文内部</t>
+  </si>
+  <si>
+    <t>需记录时</t>
+  </si>
+  <si>
+    <t>拟公开摘要、审核状态</t>
+  </si>
+  <si>
+    <t>内部日报与公开摘要分开；保存不等于发布。</t>
+  </si>
+  <si>
+    <t>批准后本团家属范围</t>
+  </si>
+  <si>
+    <t>版本、更新人及时间</t>
+  </si>
+  <si>
+    <t>保存时递增版本并记录更新人及时间；不据此声称具备防覆盖检查、逐级审批或完整文字修订历史。</t>
+  </si>
+  <si>
+    <t>系统记录</t>
+  </si>
+  <si>
+    <t>系统</t>
+  </si>
+  <si>
+    <t>保存时</t>
+  </si>
+  <si>
+    <t>客观事件记录表（草案）</t>
+  </si>
+  <si>
+    <t>已有03模板“事件记录”；S39 P86；S40 04表B14:F14。事件与学生评价分开。</t>
+  </si>
+  <si>
+    <t>团期、发生时间、类别</t>
+  </si>
+  <si>
+    <t>记录真实发生时间；按现有类别选择。</t>
+  </si>
+  <si>
+    <t>现场负责人员</t>
+  </si>
+  <si>
+    <t>发生后及时记录</t>
+  </si>
+  <si>
+    <t>相关人员、车辆范围</t>
+  </si>
+  <si>
+    <t>涉及个人时关联相应人员；团级事件按现有入口处理。</t>
+  </si>
+  <si>
+    <t>涉及个人时必填</t>
+  </si>
+  <si>
+    <t>负责人员</t>
+  </si>
+  <si>
+    <t>私人事件不跨车披露</t>
+  </si>
+  <si>
+    <t>记录时</t>
+  </si>
+  <si>
+    <t>客观经过、处置过程</t>
+  </si>
+  <si>
+    <t>填写已观察事实、已采取措施及结果；不用性格标签代替事实。</t>
+  </si>
+  <si>
+    <t>经过必填；处置发生时填</t>
+  </si>
+  <si>
+    <t>原文内部，健康细节仍受限</t>
+  </si>
+  <si>
+    <t>先按现有流程处置，再记录</t>
+  </si>
+  <si>
+    <t>从内部事件单独形成适宜公开的服务摘要，确认个人或团级范围。</t>
+  </si>
+  <si>
+    <t>负责人员拟稿</t>
+  </si>
+  <si>
+    <t>个人仅本订单；团级按批准范围</t>
+  </si>
+  <si>
+    <t>记录人、更新时间及版本</t>
+  </si>
+  <si>
+    <t>用于追溯当前事件，不能据此声称全部处置步骤历史均已实现。</t>
+  </si>
+  <si>
+    <t>阶段查询与汇总表（草案）</t>
+  </si>
+  <si>
+    <t>会议01:31:10—01:31:28；S39 P85；S40 04表D7:D8。正式汇总版式仍可调整。</t>
+  </si>
+  <si>
+    <t>团期、查看日期；范围/车辆建议</t>
+  </si>
+  <si>
+    <t>当前执行节点页可按单日期查看，导出覆盖当前整团期；日期范围或车辆筛选导出仅为后续可调整草案。</t>
+  </si>
+  <si>
+    <t>团期必需；查看日期按需</t>
+  </si>
+  <si>
+    <t>运营选择</t>
+  </si>
+  <si>
+    <t>管理负责人</t>
+  </si>
+  <si>
+    <t>阶段检查或全团期导出时</t>
+  </si>
+  <si>
+    <t>应填/已填/未填、未到名单</t>
+  </si>
+  <si>
+    <t>按计划节点当前版本×当前有效确认人员核对；已填只计明确关联该节点及版本的发生记录。未到算完成核对并单列异常，撤销不算已填；日报不自动计入。计划改版保留旧事实但不计入新版已填；无计划不报完成率。</t>
+  </si>
+  <si>
+    <t>系统汇总</t>
+  </si>
+  <si>
+    <t>查询时</t>
+  </si>
+  <si>
+    <t>执行计划、逐次历史</t>
+  </si>
+  <si>
+    <t>分别列计划节点及实际记录，含发生时间、状态、前记录引用、更正原因、版本、记录人。</t>
+  </si>
+  <si>
+    <t>明细不直接给家属</t>
+  </si>
+  <si>
+    <t>查询/导出时</t>
+  </si>
+  <si>
+    <t>逐人日报、团级日报、事件摘要</t>
+  </si>
+  <si>
+    <t>仅必要服务事实与获批摘要；排除健康、私人备注及未获准私人事件正文。</t>
+  </si>
+  <si>
+    <t>不直接公开整表</t>
+  </si>
+  <si>
+    <t>阶段结论、正式排版</t>
+  </si>
+  <si>
+    <t>结论由负责人据事实填写，正式学校/客户报表列名与打印样式另核；不宣称官方原表已还原。</t>
+  </si>
+  <si>
+    <t>按需；本稿确认项</t>
+  </si>
+  <si>
+    <t>运营/负责人</t>
+  </si>
+  <si>
+    <t>需求方指定</t>
+  </si>
+  <si>
+    <t>按确认用途</t>
+  </si>
+  <si>
+    <t>阶段汇报前</t>
+  </si>
+  <si>
+    <t>学生人工评价单（草案）</t>
+  </si>
+  <si>
+    <t>用户本轮确认；S39 P92—95；S04参考及官方评价方向。</t>
+  </si>
+  <si>
+    <t>团期、学生、班级</t>
+  </si>
+  <si>
+    <t>有效无冲突学生名单带出；教师和陪同不计入应评。</t>
+  </si>
+  <si>
+    <t>负责导游核对</t>
+  </si>
+  <si>
+    <t>学校仅必要身份列</t>
+  </si>
+  <si>
+    <t>评价时</t>
+  </si>
+  <si>
+    <t>观察记录</t>
+  </si>
+  <si>
+    <t>七项建议可编辑，按真实活动写具体表现；不要求机械逐项填写。</t>
+  </si>
+  <si>
+    <t>有权人员内部查看</t>
+  </si>
+  <si>
+    <t>不进学校报告</t>
+  </si>
+  <si>
+    <t>活动中或结束后整理</t>
+  </si>
+  <si>
+    <t>人工等级</t>
+  </si>
+  <si>
+    <t>逐人选A（优秀）或B（合格）；初始未评价，不默认、不按记录数自动计算。</t>
+  </si>
+  <si>
+    <t>每名应评学生必选</t>
+  </si>
+  <si>
+    <t>有确认权限人员</t>
+  </si>
+  <si>
+    <t>确认后学校A/B</t>
+  </si>
+  <si>
+    <t>确认整团评价前</t>
+  </si>
+  <si>
+    <t>应评/已评/未评</t>
+  </si>
+  <si>
+    <t>已评只计算非空人工A/B；仍有应评学生未评时不能整团确认。</t>
+  </si>
+  <si>
+    <t>系统计算</t>
+  </si>
+  <si>
+    <t>保存/确认时</t>
+  </si>
+  <si>
+    <t>标准版本、确认状态</t>
+  </si>
+  <si>
+    <t>先确认适用标准；评级或观察修改后重新确认，旧标准不静默变更。</t>
+  </si>
+  <si>
+    <t>系统记录/确认操作</t>
+  </si>
+  <si>
+    <t>有相应权限人员</t>
+  </si>
+  <si>
+    <t>按现有权限</t>
+  </si>
+  <si>
+    <t>学校只取已确认等级</t>
+  </si>
+  <si>
+    <t>最终确认与修改后</t>
   </si>
   <si>
     <t>学校报告</t>
   </si>
   <si>
-    <t>仅输出业务确认的A/B结果；内部观察、优秀/关注标记和负面文字不进入学校报告；正式列名、排版及文件格式请确认。</t>
-  </si>
-  <si>
-    <t>S39 P93—94；S40 04表B13:F13</t>
-  </si>
-  <si>
-    <t>家属可见</t>
-  </si>
-  <si>
-    <t>内部逐项观察默认不向家属直接展示；服务公开摘要另走审核，不与学生评价混用。</t>
-  </si>
-  <si>
-    <t>S39 P93；S40 04表F12</t>
-  </si>
-  <si>
-    <t>修改与生效</t>
-  </si>
-  <si>
-    <t>建议修改后重新确认；请填写适用课程/年级、标准版本、确认人和生效日期。仅填写本稿不自动启用系统标准。</t>
-  </si>
-  <si>
-    <t>我方建议；S39 P95</t>
-  </si>
-  <si>
-    <t>当前点名与信息核对</t>
-  </si>
-  <si>
-    <t>沿用03模板“出行点名”A2:L2；S39 P83/P85；S40 04表B6:F6。当前仅状态及最后更新时间，不是每次点名历史。</t>
-  </si>
-  <si>
-    <t>字段</t>
-  </si>
-  <si>
-    <t>字段说明/现有边界</t>
-  </si>
-  <si>
-    <t>必填建议</t>
-  </si>
-  <si>
-    <t>填写人建议</t>
-  </si>
-  <si>
-    <t>审核人建议</t>
-  </si>
-  <si>
-    <t>家属可见建议</t>
-  </si>
-  <si>
-    <t>发生节点建议</t>
-  </si>
-  <si>
-    <t>团期、当前车辆、人员引用、姓名、类型、班级</t>
-  </si>
-  <si>
-    <t>沿用原表身份列；以有效确认的人车名单核对，标识由系统带出。</t>
-  </si>
-  <si>
-    <t>必需（带出）</t>
-  </si>
-  <si>
-    <t>系统/负责导游</t>
-  </si>
-  <si>
-    <t>运营复核</t>
-  </si>
-  <si>
-    <t>默认内部</t>
-  </si>
-  <si>
-    <t>查看当前有效名单时</t>
-  </si>
-  <si>
-    <t>保留当前逐人状态；状态选项及异常说明要求请确认。</t>
-  </si>
-  <si>
-    <t>建议必填</t>
-  </si>
-  <si>
-    <t>负责导游</t>
-  </si>
-  <si>
-    <t>待甲方指定</t>
-  </si>
-  <si>
-    <t>仅必要结果，范围待确认</t>
-  </si>
-  <si>
-    <t>具体点名节点待确认</t>
-  </si>
-  <si>
-    <t>最后更新时间、更新人</t>
-  </si>
-  <si>
-    <t>显示最近一次状态更新；不能还原出发/到达/返程每次点名。</t>
-  </si>
-  <si>
-    <t>系统记录</t>
-  </si>
-  <si>
-    <t>系统</t>
-  </si>
-  <si>
-    <t>运营查看</t>
-  </si>
-  <si>
-    <t>状态更新时</t>
-  </si>
-  <si>
-    <t>日期或节点说明</t>
-  </si>
-  <si>
-    <t>原表有日期；如需每日多次点名历史属另行确认内容，不以当前状态填充历史。</t>
-  </si>
-  <si>
-    <t>待确认</t>
-  </si>
-  <si>
-    <t>次数及节点待确认</t>
-  </si>
-  <si>
-    <t>资料已核对、已入群</t>
-  </si>
-  <si>
-    <t>原表已有列；是否仍采集、何时必填请确认，不把未填当完成。</t>
-  </si>
-  <si>
-    <t>出行准备节点待确认</t>
-  </si>
-  <si>
-    <t>只记必要客观事实；健康正文不写入普通点名表。</t>
-  </si>
-  <si>
-    <t>异常时建议填</t>
-  </si>
-  <si>
-    <t>默认不公开</t>
-  </si>
-  <si>
-    <t>发现异常时</t>
-  </si>
-  <si>
-    <t>逐人每日餐宿记录</t>
-  </si>
-  <si>
-    <t>从03模板“每日报告”细化为人员+团期+日期；S39 P87—88；S40 04表B7:F8。为我方建议，不冒充甲方原表。</t>
-  </si>
-  <si>
-    <t>团期、人员、记录日期</t>
-  </si>
-  <si>
-    <t>一人一日记录；日期范围和人员归属按实际行程核对。</t>
-  </si>
-  <si>
-    <t>必需</t>
-  </si>
-  <si>
-    <t>仅本订单人员摘要</t>
-  </si>
-  <si>
-    <t>每日；提交时点待确认</t>
-  </si>
-  <si>
-    <t>记录住宿服务事实；是否需要独立查房节点/次数请确认，不预设一天三次。</t>
-  </si>
-  <si>
-    <t>适用时建议填</t>
-  </si>
-  <si>
-    <t>负责导游/获授权运营</t>
-  </si>
-  <si>
-    <t>只公开批准摘要</t>
-  </si>
-  <si>
-    <t>住宿/查房后，频次待确认</t>
-  </si>
-  <si>
-    <t>现为单一文字字段，可在同一文字注明餐次；不是早餐/午餐/晚餐三个结构化字段，不能据此统计各餐完成率。</t>
-  </si>
-  <si>
-    <t>用餐后或每日汇总，待确认</t>
-  </si>
-  <si>
-    <t>身体情况、私人备注</t>
-  </si>
-  <si>
-    <t>仅在有效家属授权、健康权限及负责范围内处理；普通管理汇总不导出原文。</t>
-  </si>
-  <si>
-    <t>按需，不强制</t>
-  </si>
-  <si>
-    <t>满足授权条件的负责人员</t>
-  </si>
-  <si>
-    <t>有权人员，待确认</t>
-  </si>
-  <si>
-    <t>不直接公开正文</t>
-  </si>
-  <si>
-    <t>需记录时；授权有效期间</t>
-  </si>
-  <si>
-    <t>拟公开摘要、审核状态</t>
-  </si>
-  <si>
-    <t>仅本人家庭可见已批准的服务摘要；修改事实后重新确认摘要，不能自动发布。</t>
-  </si>
-  <si>
-    <t>公开时建议必填</t>
-  </si>
-  <si>
-    <t>负责人员拟稿</t>
-  </si>
-  <si>
-    <t>有发布权限的人员，姓名待确认</t>
-  </si>
-  <si>
-    <t>批准后，本订单相应人员</t>
-  </si>
-  <si>
-    <t>拟公开前</t>
-  </si>
-  <si>
-    <t>最后修改时间、记录版本</t>
-  </si>
-  <si>
-    <t>用于核对当前记录和修改，不当作完整逐次查房历史。</t>
-  </si>
-  <si>
-    <t>保存或审核时</t>
-  </si>
-  <si>
-    <t>团级每日报告</t>
-  </si>
-  <si>
-    <t>沿用03模板“每日报告”A2:I2；S39 P85/P87；S40 04表B7:F8。与逐人每日记录并存。</t>
-  </si>
-  <si>
-    <t>团期编号、报告日期、填写人</t>
-  </si>
-  <si>
-    <t>标识团队每日服务记录；不能替代逐个孩子的餐宿记录。</t>
-  </si>
-  <si>
-    <t>仅批准的团级摘要</t>
-  </si>
-  <si>
-    <t>每日；截止时点待确认</t>
-  </si>
-  <si>
-    <t>记录全团住宿安排与执行事实；人员隐私放受限记录。</t>
-  </si>
-  <si>
-    <t>仅批准摘要</t>
-  </si>
-  <si>
-    <t>住宿执行后</t>
-  </si>
-  <si>
-    <t>沿用一个“用餐情况”文字栏；即使文字写三餐，也不视为三个字段或各餐历史。</t>
-  </si>
-  <si>
-    <t>身体情况、其他记录</t>
-  </si>
-  <si>
-    <t>原模板已有列；建议团级只写去标识的服务事实，个人健康正文转受限逐人记录。</t>
-  </si>
-  <si>
-    <t>按需；内容边界待确认</t>
-  </si>
-  <si>
-    <t>原文默认内部</t>
-  </si>
-  <si>
-    <t>需记录时</t>
-  </si>
-  <si>
-    <t>区分内部报告与公开版本，不以已保存等同已批准。</t>
-  </si>
-  <si>
-    <t>负责导游拟稿</t>
-  </si>
-  <si>
-    <t>有发布权限的人员，待确认</t>
-  </si>
-  <si>
-    <t>批准后团期家属范围</t>
-  </si>
-  <si>
-    <t>公开前</t>
-  </si>
-  <si>
-    <t>客观事件及公开摘要</t>
-  </si>
-  <si>
-    <t>沿用03模板“事件记录”A2:J2；S39 P86；S40 04表B14:F14。事件与评价分开，表单不代替现场处置。</t>
-  </si>
-  <si>
-    <t>团期、发生时间、事件类别</t>
-  </si>
-  <si>
-    <t>填写事件实际发生时点；类别选项由甲方确认。</t>
-  </si>
-  <si>
-    <t>现场负责人员</t>
-  </si>
-  <si>
-    <t>事件发生后及时记录</t>
-  </si>
-  <si>
-    <t>人员引用、姓名</t>
-  </si>
-  <si>
-    <t>涉及个人时填写，是否允许纯团级事件请确认；导出最小必要信息。</t>
-  </si>
-  <si>
-    <t>涉及个人时建议必填</t>
-  </si>
-  <si>
-    <t>负责人员</t>
-  </si>
-  <si>
-    <t>仅本人相关批准摘要</t>
-  </si>
-  <si>
-    <t>记录事件时</t>
-  </si>
-  <si>
-    <t>写经过和已观察事实，不用“不听话”等评价标签替代；健康细节受授权和权限限制。</t>
-  </si>
-  <si>
-    <t>原文默认不公开</t>
-  </si>
-  <si>
-    <t>及时记录；节点待确认</t>
-  </si>
-  <si>
-    <t>记已采取措施及实际结果；需紧急处置的先按现有线下流程执行。</t>
-  </si>
-  <si>
-    <t>发生处置时建议填</t>
-  </si>
-  <si>
-    <t>处置负责人员</t>
-  </si>
-  <si>
-    <t>每次必要处置后，是否留历史待确认</t>
-  </si>
-  <si>
-    <t>脱离内部正文单独形成服务摘要；明确个人或团级范围后再批准。</t>
-  </si>
-  <si>
-    <t>个人仅本订单；团级按确认范围</t>
-  </si>
-  <si>
-    <t>记录人、更新时间</t>
-  </si>
-  <si>
-    <t>用于追溯当前事件记录，不据此声称完整处置历史已实现。</t>
-  </si>
-  <si>
-    <t>管理查询、汇总与导出</t>
-  </si>
-  <si>
-    <t>我方按现有记录提出管理汇总草案；S39 P85；S40 04表D7:D8。产品是否已验收，另见本轮集成回执。</t>
-  </si>
-  <si>
-    <t>团期、日期范围、车辆筛选</t>
-  </si>
-  <si>
-    <t>限定授权范围；默认不跨机构，不把管理员身份等同健康授权。</t>
-  </si>
-  <si>
-    <t>团期必需；其余待确认</t>
-  </si>
-  <si>
-    <t>运营选择</t>
-  </si>
-  <si>
-    <t>管理负责人，待确认</t>
-  </si>
-  <si>
-    <t>不直接给家属</t>
-  </si>
-  <si>
-    <t>管理检查或导出时</t>
-  </si>
-  <si>
-    <t>当前点名状态、最后更新时间</t>
-  </si>
-  <si>
-    <t>列当前人员、车辆与状态；不显示并不存在的多次历史点名率。</t>
-  </si>
-  <si>
-    <t>系统汇总</t>
-  </si>
-  <si>
-    <t>运营核对</t>
-  </si>
-  <si>
-    <t>查询时的当前快照</t>
-  </si>
-  <si>
-    <t>逐人每日餐宿事实、批准摘要</t>
-  </si>
-  <si>
-    <t>按人+日列住宿、单一用餐文字及批准摘要；排除健康和私人备注正文。</t>
-  </si>
-  <si>
-    <t>不直接公开整表</t>
-  </si>
-  <si>
-    <t>查询或导出时</t>
-  </si>
-  <si>
-    <t>团队日报、事件摘要</t>
-  </si>
-  <si>
-    <t>管理投影只用必要事实和获准摘要，不包含其他车辆私人事件正文。</t>
-  </si>
-  <si>
-    <t>记录数、人员数、待审核数</t>
-  </si>
-  <si>
-    <t>请逐项确认统计口径及分母；记录数不等于独立人数或完成率。</t>
-  </si>
-  <si>
-    <t>管理负责人</t>
-  </si>
-  <si>
-    <t>查询时</t>
-  </si>
-  <si>
-    <t>导出人、导出时间、格式及列顺序</t>
-  </si>
-  <si>
-    <t>建议Excel导出当前筛选范围，打印样式和官方汇总表逐字段待确认。</t>
-  </si>
-  <si>
-    <t>系统信息；格式待确认</t>
+    <t>正式结果只含A/B及必要身份信息，无内部观察/健康正文；官方报告格式仍待原表核对。</t>
+  </si>
+  <si>
+    <t>按学校需要导出</t>
   </si>
   <si>
     <t>有导出权限人员</t>
   </si>
   <si>
-    <t>是否审批待确认</t>
-  </si>
-  <si>
-    <t>导出或打印时</t>
-  </si>
-  <si>
-    <t>已提供材料与尚需确认项</t>
-  </si>
-  <si>
-    <t>T为原件表序号，R为表内行；S39 P为正文段；S40按工作表名称和单元格定位。03模板是已有开发模板，不冒充甲方原表。</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>材料</t>
-  </si>
-  <si>
-    <t>准确定位/内容</t>
-  </si>
-  <si>
-    <t>本次处理</t>
-  </si>
-  <si>
-    <t>需求方补充</t>
-  </si>
-  <si>
-    <t>来源S39</t>
-  </si>
-  <si>
-    <t>《一体化业务系统_详细需求整理与确认稿_20260914.docx》</t>
-  </si>
-  <si>
-    <t>P83—88执行记录；P92—95导游评价及A/B；P99学校服务评价表。</t>
-  </si>
-  <si>
-    <t>P为正文段号；用于核对最终需求原则，不把草案当成已确认规则。</t>
-  </si>
-  <si>
-    <t>来源S40</t>
-  </si>
-  <si>
-    <t>《临安旅游集散中心_项目启动资料清单与业务调研模板_会议更新版_20260914.xlsx》</t>
-  </si>
-  <si>
-    <t>04_导游执行与评价；13_待确认事项。按表名及单元格定位。</t>
-  </si>
-  <si>
-    <t>最终待确认规则依据；保留空白确认结果，不替需求方填写同意。</t>
-  </si>
-  <si>
-    <t>已提供</t>
-  </si>
-  <si>
-    <t>S04《3.趣研学品牌介绍.docx》</t>
-  </si>
-  <si>
-    <t>T2/T3/T4：三份课程时间安排；T5：四类12观察项；T6小组合作、T7汇报单。</t>
-  </si>
-  <si>
-    <t>不重复索取；确认哪些内容保留或调整，原表自评不自动恢复。</t>
-  </si>
-  <si>
-    <t>S05《5.9 车辆联系单（衣锦一年级-大明山）.docx》</t>
-  </si>
-  <si>
-    <t>P1及T1车辆联系单，含车辆、人数、随车联系人等字段。</t>
-  </si>
-  <si>
-    <t>不重复索取本样表；本确认稿不复制真实姓名电话。</t>
-  </si>
-  <si>
-    <t>已有开发方模板</t>
-  </si>
-  <si>
-    <t>docs/templates/03-导游执行记录模板.xlsx</t>
-  </si>
-  <si>
-    <t>出行点名A2:L2；每日报告A2:I2；事件记录A2:J2。</t>
-  </si>
-  <si>
-    <t>本工作簿保留三张原模板参考页；不是甲方完整7—8张原表。</t>
+    <t>业务负责人</t>
+  </si>
+  <si>
+    <t>对应学校范围</t>
+  </si>
+  <si>
+    <t>全部评价确认后</t>
+  </si>
+  <si>
+    <t>已知材料、待确认边界与官方链接</t>
+  </si>
+  <si>
+    <t>S/T/R/P定位沿用来源核对记录。既有课程安排和车辆联系单不再索取。链接仅提供评价方向，不证明本稿为官方量表。</t>
+  </si>
+  <si>
+    <t>来源状态</t>
+  </si>
+  <si>
+    <t>材料/内容</t>
+  </si>
+  <si>
+    <t>处理口径或官方链接</t>
+  </si>
+  <si>
+    <t>本轮确认</t>
+  </si>
+  <si>
+    <t>A=优秀、B=合格；导游逐名学生手动评价</t>
+  </si>
+  <si>
+    <t>用户最新确认优先于旧批量口径；不再索取A/B名称</t>
+  </si>
+  <si>
+    <t>已提供S04</t>
+  </si>
+  <si>
+    <t>3.趣研学品牌介绍.docx：T2—4课程安排，T5四类十二项观察</t>
+  </si>
+  <si>
+    <t>十二项仅供原文参考，不新增另一套必填；疑似错字不当正式指标</t>
+  </si>
+  <si>
+    <t>已提供S05</t>
+  </si>
+  <si>
+    <t>5.9 车辆联系单（衣锦一年级-大明山）.docx</t>
+  </si>
+  <si>
+    <t>车辆、人数、联系人等已有样表；不重复索取，不复制个人电话</t>
+  </si>
+  <si>
+    <t>已提供S08</t>
+  </si>
+  <si>
+    <t>大明山（告家长书）.docx：11:30自带午餐，无住宿；P10/P12/P13安全文明</t>
+  </si>
+  <si>
+    <t>活动日程可作该团节点依据，不能泛化成所有团的必填检查点</t>
+  </si>
+  <si>
+    <t>S39/S40</t>
+  </si>
+  <si>
+    <t>详细需求整理P83—88、P92—95、P99；工作簿04表B6:F8/B12:F15</t>
+  </si>
+  <si>
+    <t>最终原则与待确认字段分开；P99学校评价旅行社服务表与学生评价不同</t>
+  </si>
+  <si>
+    <t>会议转写</t>
+  </si>
+  <si>
+    <t>01:31汇总，01:35小包团三餐/查房，01:36大包团七八张表</t>
+  </si>
+  <si>
+    <t>三次查房是小包团例子；八类草案不是全部原表已取得</t>
+  </si>
+  <si>
+    <t>官方方向</t>
+  </si>
+  <si>
+    <t>教育部研学旅行意见；浙江课程指南；综合实践活动课程指导纲要</t>
+  </si>
+  <si>
+    <t>仅支持观察方向，不是教育局官方评分表，未规定本系统A/B或自动阈值</t>
   </si>
   <si>
     <t>待逐字段确认</t>
   </si>
   <si>
-    <t>大包团其余约7—8张现行原表及小包团表</t>
-  </si>
-  <si>
-    <t>S39 P84/P88；S40 04表C7:C8、13表B11:F11。</t>
-  </si>
-  <si>
-    <t>优先提交尚未提供的官方表；也可直接修订五组建议并注明其对应原表。需确认字段、必填、填写人、审核人、公开范围和节点。</t>
-  </si>
-  <si>
-    <t>人工A/B定义、适用课程年级和正式学校导出格式</t>
-  </si>
-  <si>
-    <t>S39 P94—95；S40 04表C12:C13、13表B10:F10。</t>
-  </si>
-  <si>
-    <t>填写A/B定义和确认人/日期；权重阈值如不采用请明确写“不采用”。</t>
-  </si>
-  <si>
-    <t>待原表</t>
-  </si>
-  <si>
-    <t>学校/教育部门对旅行社服务的评价表</t>
-  </si>
-  <si>
-    <t>S39 P99；S40 04表C15。</t>
-  </si>
-  <si>
-    <t>与学生A/B报告、S04课程观察表不是同一表，不假造教育部门指标。</t>
-  </si>
-  <si>
-    <t>已有最终原则</t>
-  </si>
-  <si>
-    <t>导游主评、内部详细记录与学校结果分开</t>
-  </si>
-  <si>
-    <t>S39 P92—95；S40 04表B12:F13。</t>
-  </si>
-  <si>
-    <t>不要求学生自评；未评价不自动A；甲方确认前草案不生效。</t>
+    <t>其余尚未提供的现行执行原表、适用团型与时点、正式学校/教育部门服务评价表</t>
+  </si>
+  <si>
+    <t>也可直接修订本稿并写对应原表；已提供材料不重复索取</t>
+  </si>
+  <si>
+    <t>开发方原模板</t>
+  </si>
+  <si>
+    <t>docs/templates/03-导游执行记录模板.xlsx：出行点名/每日报告/事件记录</t>
+  </si>
+  <si>
+    <t>前三张参考页保留，不能当作甲方全部七八张表</t>
+  </si>
+  <si>
+    <t>官方链接</t>
+  </si>
+  <si>
+    <t>教育部《关于推进中小学生研学旅行的意见》</t>
+  </si>
+  <si>
+    <t>https://www.moe.gov.cn/srcsite/A06/s3325/201612/t20161219_292354.html</t>
+  </si>
+  <si>
+    <t>浙江省研学旅行课程指南（义乌市政府公开全文）</t>
+  </si>
+  <si>
+    <t>https://www.yw.gov.cn/art/2024/7/26/art_1229449113_1806769.html</t>
+  </si>
+  <si>
+    <t>浙江省研学旅行课程指南（临海市政府PDF）</t>
+  </si>
+  <si>
+    <t>https://www.linhai.gov.cn/module/download/downfile.jsp?classid=0&amp;filename=e0ac97cb6a95410c863610f854634ffa.pdf</t>
+  </si>
+  <si>
+    <t>教育部《中小学综合实践活动课程指导纲要》</t>
+  </si>
+  <si>
+    <t>https://www.moe.gov.cn/srcsite/A26/s8001/201710/t20171017_316616.html</t>
   </si>
 </sst>
 </file>
@@ -2730,21 +3000,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="23" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2756,7 +3027,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2768,51 +3039,51 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>237</v>
+        <v>175</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>35</v>
@@ -2820,25 +3091,25 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>35</v>
@@ -2846,25 +3117,25 @@
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>26</v>
+        <v>231</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>35</v>
@@ -2872,25 +3143,25 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>27</v>
+        <v>235</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>162</v>
+        <v>237</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>35</v>
@@ -2898,58 +3169,32 @@
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>253</v>
+        <v>177</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H8"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -2970,18 +3215,19 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="23" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -2993,7 +3239,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>257</v>
+        <v>244</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -3005,77 +3251,77 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>261</v>
+        <v>175</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>262</v>
+        <v>176</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="58" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>157</v>
+        <v>251</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>35</v>
@@ -3083,25 +3329,25 @@
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>268</v>
+        <v>176</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>35</v>
@@ -3109,25 +3355,25 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>35</v>
@@ -3135,25 +3381,25 @@
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>276</v>
+        <v>263</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>278</v>
-      </c>
       <c r="F8" s="7" t="s">
-        <v>157</v>
+        <v>268</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>35</v>
@@ -3161,25 +3407,25 @@
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>284</v>
+        <v>198</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>35</v>
@@ -3204,209 +3450,1106 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="65" customWidth="1"/>
-    <col min="5" max="5" width="35" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-    </row>
-    <row r="2" ht="48" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>288</v>
       </c>
+      <c r="B7" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L确认草案｜未正式生效&amp;C&amp;A&amp;R第 &amp;P 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>165</v>
+      </c>
       <c r="B3" s="6" t="s">
-        <v>289</v>
+        <v>166</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>290</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>291</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>293</v>
       </c>
+      <c r="D8" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L确认草案｜未正式生效&amp;C&amp;A&amp;R第 &amp;P 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>320</v>
+      </c>
       <c r="B4" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="74" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>294</v>
       </c>
+      <c r="E5" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H8"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L确认草案｜未正式生效&amp;C&amp;A&amp;R第 &amp;P 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>347</v>
+      </c>
       <c r="C4" s="7" t="s">
-        <v>295</v>
+        <v>174</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>297</v>
+        <v>351</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>298</v>
+        <v>352</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>299</v>
+        <v>193</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>302</v>
+        <v>357</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>303</v>
+        <v>358</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>301</v>
+        <v>362</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>305</v>
+        <v>363</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>309</v>
+        <v>367</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>313</v>
+        <v>374</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:H9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
+  <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L确认草案｜未正式生效&amp;C&amp;A&amp;R第 &amp;P 页</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="74" customWidth="1"/>
+    <col min="3" max="3" width="100" customWidth="1"/>
+    <col min="4" max="4" width="35" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>173</v>
+        <v>403</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>319</v>
+        <v>406</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>320</v>
+        <v>407</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>323</v>
+        <v>409</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E12" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E12"/>
+  <autoFilter ref="A3:D16"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4284,12 +5427,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="95" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="112" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -4328,7 +5471,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" ht="58" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>36</v>
       </c>
@@ -4339,7 +5482,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" ht="58" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>38</v>
       </c>
@@ -4350,7 +5493,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" ht="58" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>40</v>
       </c>
@@ -4361,7 +5504,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" ht="58" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>42</v>
       </c>
@@ -4372,7 +5515,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" ht="74" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>44</v>
       </c>
@@ -4405,30 +5548,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:C13"/>
+  <autoFilter ref="A3:C11"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -4446,343 +5567,148 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="7" width="16" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2" ht="48" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B5" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="C5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="D7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C8" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="B9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="C10" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:G15"/>
+  <autoFilter ref="A3:D10"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4800,16 +5726,16 @@
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="48" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -4818,7 +5744,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -4827,30 +5753,30 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>35</v>
@@ -4861,13 +5787,13 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>35</v>
@@ -4878,13 +5804,13 @@
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>35</v>
@@ -4895,13 +5821,13 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>35</v>
@@ -4912,13 +5838,13 @@
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>35</v>
@@ -4929,13 +5855,13 @@
     </row>
     <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>35</v>
@@ -4946,13 +5872,13 @@
     </row>
     <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>134</v>
+        <v>100</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>35</v>
@@ -4963,13 +5889,13 @@
     </row>
     <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>35</v>
@@ -4980,13 +5906,13 @@
     </row>
     <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>35</v>
@@ -5014,229 +5940,260 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="70" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D11" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="E11" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="E12" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="B13" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E13" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="C14" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="D14" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="E14" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="B15" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="C15" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="D15" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="H9" s="8" t="s">
+      <c r="E15" s="8" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:E15"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -5251,21 +6208,22 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="23" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5277,7 +6235,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5289,51 +6247,51 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>35</v>
@@ -5341,25 +6299,25 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>15</v>
+        <v>179</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>35</v>
@@ -5367,25 +6325,25 @@
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>185</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>190</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>195</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>35</v>
@@ -5393,25 +6351,25 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>35</v>
@@ -5419,58 +6377,32 @@
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H8"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -5491,18 +6423,19 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="64" customWidth="1"/>
-    <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="5" width="23" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="62" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="7" max="7" width="29" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -5514,7 +6447,7 @@
     </row>
     <row r="2" ht="48" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -5526,51 +6459,51 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>35</v>
@@ -5578,25 +6511,25 @@
     </row>
     <row r="5" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>15</v>
+        <v>206</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>161</v>
+        <v>209</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>220</v>
+        <v>177</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>35</v>
@@ -5604,25 +6537,25 @@
     </row>
     <row r="6" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>35</v>
@@ -5630,25 +6563,25 @@
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>35</v>
@@ -5656,25 +6589,25 @@
     </row>
     <row r="8" ht="42" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>35</v>
